--- a/docs/packinbag_버튼_알림_점검표.xlsx
+++ b/docs/packinbag_버튼_알림_점검표.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'버튼 목록'!$A$1:$H$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'발견된 이슈'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'발견된 이슈'!$A$1:$F$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7557,7 +7557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8050,8 +8050,68 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>AppShell &gt; 메인 탭 좌우 스와이프가 설정 탭 하위화면에서도 작동</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>팩/홈/설정 3개 메인 탭 사이 좌우 스와이프 전환 자체는 정상이지만, 설정 탭 안에서 하위 화면(프로필 수정, 화면설정, 팩 설정, 버전 정보, 라이선스, 공지사항 관리, 이용권 코드 관리)을 보고 있을 때도 이 스와이프가 계속 살아있어서, 화면 중간에서 좌우로 쓸어넘기면 뒤로가기가 아니라 다른 메인 탭(홈/팩)으로 튀어버렸습니다.</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>SettingsScreen이 하위 화면 진입 여부를 AppShell에 알리도록 콜백 추가, 하위 화면일 때는 메인 탭 전환 스와이프를 무시하도록 수정 (엣지 스와이프 뒤로가기는 그대로 유지)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>수정완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>BagEditorScreen &gt; 자동저장 디바운스 대기 중 나가면 변경사항 소실</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>가방(기존 가방) 안에서 수정하면 0.5초 후 자동으로 저장되는데, 그 0.5초가 지나기 전에 뒤로가기/스와이프로 화면을 나가면 대기 중이던 저장이 취소만 되고 다시 실행되지 않아 방금 한 수정이 조용히 사라졌습니다. PackLibraryEditorScreen에는 나갈 때 대기 중인 저장을 즉시 실행하는 안전장치가 있었는데 BagEditorScreen에는 빠져 있었습니다.</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>화면이 사라질 때(언마운트) 대기 중인 자동저장이 있으면 그 즉시 저장을 실행하도록 추가, 저장 성공/실패를 토스트로 알림 ("나가기 전 변경사항을 저장했어요")</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>수정완료</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>